--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/ILLINOIS_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/ILLINOIS_2013.xlsx
@@ -2407,7 +2407,7 @@
         <v>80</v>
       </c>
       <c r="D114">
-        <v>0.000981631225689</v>
+        <v>0.0009816312256890002</v>
       </c>
     </row>
     <row r="115">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C136">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C230">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C835">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C990">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C991">
@@ -19248,7 +19248,7 @@
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1050">
@@ -27589,7 +27589,7 @@
         <v>80</v>
       </c>
       <c r="D1513">
-        <v>0.000981631225689</v>
+        <v>0.0009816312256890002</v>
       </c>
     </row>
     <row r="1514">
@@ -27708,7 +27708,7 @@
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1520">
@@ -28464,7 +28464,7 @@
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1562">
@@ -31434,7 +31434,7 @@
       </c>
       <c r="B1727" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1727">
